--- a/smee/data/reporte-electoral.xlsx
+++ b/smee/data/reporte-electoral.xlsx
@@ -14,11 +14,11 @@
     <sheet name="Fuentes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Eventos'!$A$1:$P$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Publicaciones'!$A$1:$P$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actores'!$A$1:$G$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Revisión manual'!$A$1:$G$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Fuentes'!$A$1:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Eventos'!$A$1:$P$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Publicaciones'!$A$1:$P$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actores'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Revisión manual'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Fuentes'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventosTable" displayName="EventosTable" ref="A1:P14" headerRowCount="1">
-  <autoFilter ref="A1:P14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventosTable" displayName="EventosTable" ref="A1:P20" headerRowCount="1">
+  <autoFilter ref="A1:P20"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Código"/>
@@ -215,8 +215,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="PublicacionesTable" displayName="PublicacionesTable" ref="A1:P25" headerRowCount="1">
-  <autoFilter ref="A1:P25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="PublicacionesTable" displayName="PublicacionesTable" ref="A1:P51" headerRowCount="1">
+  <autoFilter ref="A1:P51"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Código del evento"/>
@@ -240,8 +240,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ActoresTable" displayName="ActoresTable" ref="A1:G4" headerRowCount="1">
-  <autoFilter ref="A1:G4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ActoresTable" displayName="ActoresTable" ref="A1:G3" headerRowCount="1">
+  <autoFilter ref="A1:G3"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Código del evento"/>
     <tableColumn id="2" name="Evento"/>
@@ -256,8 +256,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RevisionTable" displayName="RevisionTable" ref="A1:G13" headerRowCount="1">
-  <autoFilter ref="A1:G13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RevisionTable" displayName="RevisionTable" ref="A1:G32" headerRowCount="1">
+  <autoFilter ref="A1:G32"/>
   <tableColumns count="7">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Título"/>
@@ -272,8 +272,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FuentesTable" displayName="FuentesTable" ref="A1:H10" headerRowCount="1">
-  <autoFilter ref="A1:H10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FuentesTable" displayName="FuentesTable" ref="A1:H14" headerRowCount="1">
+  <autoFilter ref="A1:H14"/>
   <tableColumns count="8">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fuente"/>
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260801-773DCE01</t>
+          <t>SMEE-20260801-FC0313F6</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Instituto Nacional Electoral: número: 330 El inicio está previsto para el próximo 10 de septiembre, acompañado de la observación electoral. El asunto electoral principal corresponde a la publicación de un calendario electoral en Nacional, con referencia directa a ningún partido identificado, dentro del proceso electoral de 2026-2027; estos datos delimitan el alcance territorial, partidista y temporal del hecho reportado.</t>
+          <t>Instituto Nacional Electoral: número: 330 El inicio está previsto para el próximo 10 de septiembre. La información se inscribe en la publicación de un calendario electoral en Nacional, involucrando a ningún partido identificado en el ciclo electoral de 2026-2027.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -714,11 +714,11 @@
         <v>46235.00425925926</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>46234.41584490741</v>
+        <v>46235.00425925926</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>updated</t>
+          <t>detected</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="O2" s="2">
-        <f>COUNTIF('Publicaciones'!$B$2:$B$25,B2)</f>
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B2)</f>
         <v/>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -751,112 +751,104 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-87D95F84</t>
+          <t>SMEE-20260802-8E279CC1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Fasci no logra inscribirse como candidato del PAN</t>
+          <t>Cuatro finalistas de Morena avanzan a la encuesta estatal en CDMX</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Aldo Fasci falla en su intento de inscribirse, de manera extemporánea, como candidato en el PAN estatal; lo remiten al CEN albiazul. El asunto electoral principal corresponde a un registro o anuncio de candidatura en Nuevo León, con referencia directa a PAN, dentro del proceso electoral de 2027; estos datos delimitan el alcance territorial, partidista y temporal del hecho reportado.</t>
+          <t>Cuatro finalistas de Morena avanzan a la encuesta estatal en CDMX. Esta información se inscribe en una encuesta de preferencias electorales en Ciudad de México, involucrando a Morena en el ciclo 2027 según lo publicado por la fuente consultada.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Registro o anuncio de candidatura</t>
+          <t>Nueva encuesta</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Nuevo León</t>
+          <t>Ciudad de México</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="3" t="n">
-        <v>46234.59326388889</v>
+        <v>46236.95389979167</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>46234.54726723379</v>
+        <v>46236.95389979167</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>updated</t>
+          <t>detected</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>Medio</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Aldo Fasci</t>
-        </is>
-      </c>
+      <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2">
-        <f>COUNTIF('Publicaciones'!$B$2:$B$25,B3)</f>
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B3)</f>
         <v/>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Tipo 'Registro o anuncio de candidatura': +8 · Actor prioritario: +4</t>
+          <t>Tipo 'Nueva encuesta': +8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-4E465D4E</t>
+          <t>SMEE-20260802-9DEC0C3C</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>PAN lidera intención de voto para gubernatura de Querétaro 2027</t>
+          <t>Nuevo León: morenistas inician contienda por gubernatura 2027</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>PAN lidera intención de voto para gubernatura de Querétaro 2027. El asunto electoral principal corresponde a una encuesta de preferencias electorales en Querétaro, con referencia directa a PAN y Morena, dentro del proceso electoral de 2027; estos datos delimitan el alcance territorial, partidista y temporal del hecho reportado.</t>
+          <t>Cuatro aspirantes de Morena compiten por la candidatura a la gubernatura en un entorno electoral atípico. Este acontecimiento se relaciona con un registro o anuncio de candidatura en Nuevo León; los actores vinculados son Morena, en la ruta electoral de 2027.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nueva encuesta</t>
+          <t>Registro o anuncio de candidatura</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Querétaro</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Querétaro</t>
-        </is>
-      </c>
+          <t>Nuevo León</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n"/>
       <c r="H4" s="3" t="n">
-        <v>46234.14221928241</v>
+        <v>46236.71268537037</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>46234.14221928241</v>
+        <v>46236.71268537037</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -878,50 +870,54 @@
       </c>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2">
-        <f>COUNTIF('Publicaciones'!$B$2:$B$25,B4)</f>
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B4)</f>
         <v/>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Tipo 'Nueva encuesta': +8</t>
+          <t>Tipo 'Registro o anuncio de candidatura': +8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-3D11F8C8</t>
+          <t>SMEE-20260801-9279F5F3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Morena y PT definirán alianza electoral en Baja California</t>
+          <t>Morena define rumbo en Michoacán para candidatura gubernamental</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Morena y PT definirán alianza electoral en Baja California. El asunto electoral principal corresponde a una coalición o alianza electoral en Baja California, con referencia directa a Morena y Partido del Trabajo, dentro del proceso electoral de 2027; estos datos delimitan el alcance territorial, partidista y temporal del hecho reportado.</t>
+          <t>Morena define rumbo en Michoacán para candidatura gubernamental. Este acontecimiento se relaciona con un registro o anuncio de candidatura en Michoacán; los actores vinculados son Morena, en la ruta electoral de 2027 según lo publicado por la fuente consultada.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Coalición o alianza</t>
+          <t>Registro o anuncio de candidatura</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Baja California</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n"/>
+          <t>Michoacán</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Morelia</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="n">
-        <v>46234.03368690972</v>
+        <v>46235.84953381945</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>46234.03368690972</v>
+        <v>46235.84953381945</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -934,63 +930,59 @@
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2">
-        <f>COUNTIF('Publicaciones'!$B$2:$B$25,B5)</f>
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B5)</f>
         <v/>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Tipo 'Coalición o alianza': +7</t>
+          <t>Tipo 'Registro o anuncio de candidatura': +8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260730-4E0930D8</t>
+          <t>SMEE-20260803-910904DC</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Somos México impugna reforma electoral en San Luis Potosí</t>
+          <t>Colosio y Astiazarán buscan alianza en la gubernatura de Sonora</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Somos México impugna reforma electoral en San Luis Potosí. El asunto electoral principal corresponde a una impugnación electoral en San Luis Potosí, con referencia directa a ningún partido identificado, dentro del proceso electoral de 2027; estos datos delimitan el alcance territorial, partidista y temporal del hecho reportado.</t>
+          <t>Colosio y Astiazarán buscan alianza en la gubernatura de Sonora. Este evento corresponde a un hecho relacionado con el proceso electoral en Sonora, donde se identifica a ningún partido identificado dentro del calendario electoral de 2027.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Impugnación</t>
+          <t>Otro evento electoral</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>San Luis Potosí</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>San Luis Potosí</t>
-        </is>
-      </c>
+          <t>Sonora</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" s="3" t="n">
-        <v>46233.34743726852</v>
+        <v>46237.68370269676</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>46233.34743726852</v>
+        <v>46237.68370269676</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -999,11 +991,11 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Medio</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -1012,12 +1004,12 @@
       </c>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2">
-        <f>COUNTIF('Publicaciones'!$B$2:$B$25,B6)</f>
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B6)</f>
         <v/>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Tipo 'Impugnación': +7</t>
+          <t>Tipo 'Otro evento electoral': +3</t>
         </is>
       </c>
     </row>
@@ -1027,17 +1019,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260801-ACCA2EA0</t>
+          <t>SMEE-20260803-9A509C17</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Morena reúne a aspirantes a la gubernatura de Chihuahua para 2027</t>
+          <t>Mario García espera los tiempos para definir su futuro político</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Morena reúne a aspirantes a la gubernatura de Chihuahua para 2027. El asunto electoral principal corresponde a un hecho relacionado con el proceso electoral en Chihuahua, con referencia directa a Morena, dentro del proceso electoral de 2027; estos datos delimitan el alcance territorial, partidista y temporal del hecho reportado.</t>
+          <t>Mario García espera los tiempos para definir su futuro político. El hecho se ubica en el contexto de un hecho relacionado con el proceso electoral en Chihuahua, con mención de PAN, en el proceso electoral de 2027.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1056,10 +1048,10 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>46235.04445185185</v>
+        <v>46237.66061265046</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>46235.04445185185</v>
+        <v>46237.66061265046</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -1081,7 +1073,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2">
-        <f>COUNTIF('Publicaciones'!$B$2:$B$25,B7)</f>
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B7)</f>
         <v/>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1096,17 +1088,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-88FCC4FB</t>
+          <t>SMEE-20260803-7A52522F</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Morena reúne a nueve aspirantes en CDMX para candidatura en Sinaloa</t>
+          <t>Evaluarán votación en Ceresos para elecciones de 2027 en Chihuahua</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Morena reúne a nueve aspirantes en CDMX para candidatura en Sinaloa. El asunto electoral principal corresponde a un hecho relacionado con el proceso electoral en Sinaloa, con referencia directa a Morena, dentro del proceso electoral de 2027; estos datos delimitan el alcance territorial, partidista y temporal del hecho reportado.</t>
+          <t>Evaluarán votación en Ceresos para elecciones de 2027 en Chihuahua. Este evento corresponde a un hecho relacionado con el proceso electoral en Chihuahua, donde se identifica a PAN dentro del calendario electoral de 2027 según lo publicado por la fuente consultada.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1116,15 +1108,19 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Sinaloa</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n"/>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="H8" s="3" t="n">
-        <v>46234.91964240741</v>
+        <v>46237.6432125</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>46234.91964240741</v>
+        <v>46237.6432125</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1146,7 +1142,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2">
-        <f>COUNTIF('Publicaciones'!$B$2:$B$25,B8)</f>
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B8)</f>
         <v/>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1161,17 +1157,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-6A2B860E</t>
+          <t>SMEE-20260803-A2EAB4CA</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Mayra Chavez asume mesa de seguridad en Juárez a días de su candidatura</t>
+          <t>David Cortés impulsa alianzas y unidad en el PAN de Morelia</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Mayra Chavez asume mesa de seguridad en Juárez a días de su candidatura. El asunto electoral principal corresponde a un hecho relacionado con el proceso electoral en Chihuahua, con referencia directa a Morena, dentro del proceso electoral de 2027; estos datos delimitan el alcance territorial, partidista y temporal del hecho reportado.</t>
+          <t>David Cortés impulsa alianzas y unidad en el PAN de Morelia. Este evento corresponde a un hecho relacionado con el proceso electoral en Michoacán, donde se identifica a PAN dentro del calendario electoral de 2027.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1181,19 +1177,19 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Chihuahua</t>
+          <t>Michoacán</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Chihuahua</t>
+          <t>Morelia</t>
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>46234.76438589121</v>
+        <v>46237.60846872685</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>46234.76438589121</v>
+        <v>46237.60846872685</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1210,12 +1206,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2">
-        <f>COUNTIF('Publicaciones'!$B$2:$B$25,B9)</f>
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B9)</f>
         <v/>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1226,21 +1222,21 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-2A40DFFA</t>
+          <t>SMEE-20260803-21D35497</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Coahuila: incertidumbre en la alianza PRI-UDC para 2027</t>
+          <t>“No son tiempos”: Colosio Riojas descarta adelantarse rumbo a una posible candidatura; informará decisión a finales de 2026, dice</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Coahuila: incertidumbre en la alianza PRI-UDC para 2027. El asunto electoral principal corresponde a un hecho relacionado con el proceso electoral en Coahuila, con referencia directa a PRI, dentro del proceso electoral de 2027; estos datos delimitan el alcance territorial, partidista y temporal del hecho reportado.</t>
+          <t>El senador de Movimiento Ciudadano, Luis Donaldo Colosio Riojas. El hecho se ubica en el contexto de un hecho relacionado con el proceso electoral en Nuevo León, con mención de Movimiento Ciudadano, en el proceso electoral de 2026.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1250,15 +1246,15 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Coahuila</t>
+          <t>Nuevo León</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="3" t="n">
-        <v>46234.49685028935</v>
+        <v>46237.59851851852</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>46234.49685028935</v>
+        <v>46237.59851851852</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1275,12 +1271,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2">
-        <f>COUNTIF('Publicaciones'!$B$2:$B$25,B10)</f>
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B10)</f>
         <v/>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1291,43 +1287,43 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-6059CD3E</t>
+          <t>SMEE-20260803-E6C5BB3F</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Fracturas en la alianza Morena-PVEM crean incertidumbre electoral</t>
+          <t>Ulises Mejía Haro consolida ventaja hacia gubernatura | El Universal</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Fracturas en la alianza Morena-PVEM crean incertidumbre electoral. El asunto electoral principal corresponde a un hecho relacionado con el proceso electoral en Colima, con referencia directa a Morena, Partido Verde y Partido del Trabajo, dentro del proceso electoral de 2027; estos datos delimitan el alcance territorial, partidista y temporal del hecho reportado.</t>
+          <t>Lee también Zacatecas, Puebla y Chiapas con más crecimiento de compradores de autos nuevos. El hecho ocurre en el marco de un registro o anuncio de candidatura en Zacatecas, con la participación de PRI, Morena, Movimiento Ciudadano y Partido del Trabajo de cara al proceso de 2027.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Otro evento electoral</t>
+          <t>Registro o anuncio de candidatura</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Colima</t>
+          <t>Zacatecas</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Colima</t>
+          <t>Zacatecas</t>
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>46234.38057318287</v>
+        <v>46237.59500083554</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>46234.38057318287</v>
+        <v>46237.59500083554</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1349,32 +1345,32 @@
       </c>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2">
-        <f>COUNTIF('Publicaciones'!$B$2:$B$25,B11)</f>
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B11)</f>
         <v/>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Tipo 'Otro evento electoral': +3</t>
+          <t>Tipo 'Registro o anuncio de candidatura': +8 · Publicación duplicada vinculada: -5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-1918B7EB</t>
+          <t>SMEE-20260803-8F80E3E5</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Cambios en el gobierno estatal de Coahuila anticipan precampañas</t>
+          <t>PAN define estrategias electorales: Santiago De la Peña para Chihuahua</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Cambios en el gobierno estatal de Coahuila anticipan precampañas. El asunto electoral principal corresponde a un hecho relacionado con el proceso electoral en Coahuila, con referencia directa a PRI y Morena, dentro del proceso electoral de 2024; estos datos delimitan el alcance territorial, partidista y temporal del hecho reportado.</t>
+          <t>PAN define estrategias electorales: Santiago De la Peña para Chihuahua. La información se inscribe en un hecho relacionado con el proceso electoral en Chihuahua, involucrando a PAN en el ciclo electoral de 2027 según lo publicado por la fuente consultada.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1384,15 +1380,19 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Coahuila</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n"/>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="H12" s="3" t="n">
-        <v>46234.14085893518</v>
+        <v>46237.57703354167</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>46234.14085893518</v>
+        <v>46237.57703354167</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2">
-        <f>COUNTIF('Publicaciones'!$B$2:$B$25,B12)</f>
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B12)</f>
         <v/>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1425,21 +1425,21 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260730-0FCDBCDD</t>
+          <t>SMEE-20260803-79036C52</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Recortes presupuestales debilitan OPLE para elecciones 2027</t>
+          <t>Candidaturas de Morena se afianzan en Chihuahua con nuevos registros</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Recortes presupuestales debilitan OPLE para elecciones 2027. El asunto electoral principal corresponde a un hecho relacionado con el proceso electoral en Colima, con referencia directa a ningún partido identificado, dentro del proceso electoral de 2027; estos datos delimitan el alcance territorial, partidista y temporal del hecho reportado.</t>
+          <t>Candidaturas de Morena se afianzan en Chihuahua con nuevos registros. El hecho se ubica en el contexto de un hecho relacionado con el proceso electoral en Chihuahua, con mención de PAN y Morena, en el proceso electoral de 2024.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1449,19 +1449,19 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Colima</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Colima</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>46233.3806449537</v>
+        <v>46237.42397607639</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>46233.3806449537</v>
+        <v>46237.42397607639</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2">
-        <f>COUNTIF('Publicaciones'!$B$2:$B$25,B13)</f>
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B13)</f>
         <v/>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1494,21 +1494,21 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260730-0DBCEBC0</t>
+          <t>SMEE-20260803-F0C70DA7</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>INE solicita más de 36 mil millones de pesos para elecciones 2027</t>
+          <t>Morena establece nueva evaluación de candidatos para 2027</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Instituto Nacional Electoral: iNE solicita más de 36 mil millones de pesos para elecciones 2027. El asunto electoral principal corresponde a un hecho relacionado con el proceso electoral en Nacional, con referencia directa a ningún partido identificado, dentro del proceso electoral de 2027; estos datos delimitan el alcance territorial, partidista y temporal del hecho reportado.</t>
+          <t>Morena establece nueva evaluación de candidatos para 2027. La información se inscribe en un hecho relacionado con el proceso electoral en Puebla, involucrando a Morena en el ciclo electoral de 2027 según lo publicado por la fuente consultada.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1518,15 +1518,19 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n"/>
+          <t>Puebla</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="H14" s="3" t="n">
-        <v>46233.2014409375</v>
+        <v>46237.30557045139</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>46233.2014409375</v>
+        <v>46237.30557045139</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1546,24 +1550,426 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2">
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B14)</f>
+        <v/>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Tipo 'Otro evento electoral': +3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260803-C31C484D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Andrés Manuel López Beltrán recorre Distrito 6 de Tabasco</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Andrés Manuel López Beltrán recorre Distrito 6 de Tabasco. El hecho se ubica en el contexto de un hecho relacionado con el proceso electoral en Tabasco, con mención de Morena, en el proceso electoral de 2027.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Otro evento electoral</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="3" t="n">
+        <v>46237.23529333333</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>46237.23529333333</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>detected</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2">
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B15)</f>
+        <v/>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Tipo 'Otro evento electoral': +3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260803-C9DFFDB0</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Andy López Beltrán inicia su camino hacia diputación federal en Tabasco</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Andy López Beltrán inicia su camino hacia diputación federal en Tabasco. Este evento corresponde a un hecho relacionado con el proceso electoral en Tabasco, donde se identifica a Morena dentro del calendario electoral de 2027.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Otro evento electoral</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="3" t="n">
+        <v>46237.06389490741</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>46237.06389490741</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>detected</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2">
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B16)</f>
+        <v/>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Tipo 'Otro evento electoral': +3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260803-DF903415</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Torres Piña consolida su liderazgo en Morelia con 2 mil asistentes</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>La reunión demuestra la capacidad organizativa de Torres Piña, crucial para el futuro electoral en Michoacán. El hecho se ubica en el contexto de un hecho relacionado con el proceso electoral en Michoacán, con mención de ningún partido identificado, en el proceso electoral de 2027.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Otro evento electoral</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Morelia</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>46237.0555790625</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>46237.0555790625</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>detected</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2">
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B17)</f>
+        <v/>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Tipo 'Otro evento electoral': +3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260802-5E507918</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Unidad interna en Morena busca fortalecer candidatura en Chihuahua</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Unidad interna en Morena busca fortalecer candidatura en Chihuahua. Este evento corresponde a un hecho relacionado con el proceso electoral en Chihuahua, donde se identifica a Morena dentro del calendario electoral de 2027 según lo publicado por la fuente consultada.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Otro evento electoral</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>46236.4322178588</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>46236.4322178588</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>detected</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2">
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B18)</f>
+        <v/>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Tipo 'Otro evento electoral': +3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260803-49BC2B07</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Los gobernadores que ya eligieron a su sucesor para 2027: quiénes son los respaldados en los estados</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>El catedrático de la Universidad de la Ciénega del Estado de Michoacán (UCEMICH) señala que antes –en la época de la hegemonía del PRI– los mandatarios “tenían mano” en la elección de sus sucesores. Este evento corresponde a un hecho relacionado con el proceso electoral en Michoacán, donde se identifica a PRI y Morena dentro del calendario electoral de 2027.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Otro evento electoral</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="3" t="n">
+        <v>46237.59498476415</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>46237.59498476415</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>detected</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Descartable</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2">
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B19)</f>
+        <v/>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Tipo 'Otro evento electoral': +3 · Publicación duplicada vinculada: -5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260803-5A7E410C</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Morena se reúne con aspirantes a candidaturas para gobernador de Chihuahua, Sinaloa, Sonora y BC</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Instituto Nacional Electoral: lee también Gobierno abre consulta para proteger derechos de las audiencias en radio y televisión. La información se inscribe en un hecho relacionado con el proceso electoral en Chihuahua, involucrando a PAN, PRI y Morena en el ciclo electoral de 2027.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Otro evento electoral</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>46237.59498217774</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>46237.59498217774</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>detected</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Descartable</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>Instituto Nacional Electoral</t>
         </is>
       </c>
-      <c r="O14" s="2">
-        <f>COUNTIF('Publicaciones'!$B$2:$B$25,B14)</f>
+      <c r="O20" s="2">
+        <f>COUNTIF('Publicaciones'!$B$2:$B$51,B20)</f>
         <v/>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Tipo 'Otro evento electoral': +3</t>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Tipo 'Otro evento electoral': +3 · Publicación duplicada vinculada: -5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P14"/>
-  <conditionalFormatting sqref="K2:K14">
+  <autoFilter ref="A1:P20"/>
+  <conditionalFormatting sqref="K2:K20">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>K2="Alto"</formula>
     </cfRule>
@@ -1587,7 +1993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1692,7 +2098,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="inlineStr">
@@ -1702,11 +2108,11 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Aprueba Comisión de Vinculación el calendario de entrevistas para personas aspirantes a Presidencias y Consejerías Electorales de Organismos Públicos Locales</t>
+          <t>Entrevista del Consejero Electoral Uuc-kib Espadas con Carlos Zúñiga para Milenio TV</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46235.06549768519</v>
+        <v>46237.84706018519</v>
       </c>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
@@ -1735,7 +2141,7 @@
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2026/07/31/aprueba-comision-de-vinculacion-el-calendario-de-entrevistas-para-personas-aspirantes-a-presidencias-y-consejerias-electorales-de-organismos-publicos-locales/</t>
+          <t>https://centralelectoral.ine.mx/2026/08/03/entrevista-del-consejero-electoral-uuc-kib-espadas-con-carlos-zuniga-para-milenio-tv-5/</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -1746,13 +2152,9 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>SMEE-20260801-ACCA2EA0</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>El Congresista</t>
@@ -1760,50 +2162,38 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Morena reúne a aspirantes a la gubernatura de Chihuahua para 2027</t>
+          <t>Morena definirá coordinador de la 4T en Sonora a finales de agosto</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46235.04445185185</v>
+        <v>46237.76350483796</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Chihuahua</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Chihuahua</t>
-        </is>
-      </c>
+          <t>Sonora</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Morena</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Otro evento electoral</t>
-        </is>
-      </c>
+      <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>classified</t>
+          <t>review</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>primary_evidence</t>
-        </is>
-      </c>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1813,43 +2203,43 @@
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/chihuahua/morena-reune-aspirantes-gubernatura-chihuahua-2027</t>
+          <t>https://elcongresista.mx/politica/sonora/morena-sonora-encuesta-coordinador-agosto</t>
         </is>
       </c>
       <c r="P3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260801-773DCE01</t>
+          <t>SMEE-20260803-910904DC</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Central Electoral INE</t>
+          <t>El Congresista</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Planeará y organizará INE más de 500 actividades del Proceso Electoral Federal 2026‑2027</t>
+          <t>Colosio y Astiazarán buscan alianza en la gubernatura de Sonora</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46235.00425925926</v>
+        <v>46237.68370269676</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Sonora</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Publicación oficial de calendario electoral</t>
+          <t>Otro evento electoral</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1879,18 +2269,14 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2026/07/31/planeara-y-organizara-ine-mas-de-500-actividades-del-proceso-electoral-federal-2026%e2%80%912027/</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>INE</t>
-        </is>
-      </c>
+          <t>https://elcongresista.mx/politica/sonora/colosio-astiazaran-alianza-gubernatura-sonora</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
@@ -1900,20 +2286,20 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Entrevista del Consejero Electoral Uuc-kib Espadas con Verónica Méndez para W Radio</t>
+          <t>Invita INE Michoacán a la ciudadanía a recoger su Credencial para Votar</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46234.92717592593</v>
-      </c>
-      <c r="F5" s="2" t="n"/>
+        <v>46237.66666666666</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Otro evento electoral</t>
-        </is>
-      </c>
+      <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>review</t>
@@ -1937,51 +2323,75 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2026/07/31/entrevista-del-consejero-electoral-uuc-kib-espadas-con-veronica-mendez-para-w-radio/</t>
+          <t>https://centralelectoral.ine.mx/2026/08/03/invita-ine-michoacan-a-la-ciudadania-a-recoger-su-credencial-para-votar/</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>INE</t>
+          <t>Redacción INE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260803-9A509C17</t>
+        </is>
+      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Central Electoral INE</t>
+          <t>El Congresista</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Entrevista del Consejero Electoral Uuc-kib Espadas con Salvador García Soto para «A la una»</t>
+          <t>Mario García espera los tiempos para definir su futuro político</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46234.91991898148</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
+        <v>46237.66061265046</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>PAN</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Otro evento electoral</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>classified</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>primary_evidence</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1991,22 +2401,18 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2026/07/31/entrevista-del-consejero-electoral-uuc-kib-espadas-con-salvador-garcia-soto-para-a-la-una/</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>INE</t>
-        </is>
-      </c>
+          <t>https://elcongresista.mx/politica/chihuahua/mario-garcia-2027</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-88FCC4FB</t>
+          <t>SMEE-20260803-7A52522F</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2016,21 +2422,25 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Morena reúne a nueve aspirantes en CDMX para candidatura en Sinaloa</t>
+          <t>Evaluarán votación en Ceresos para elecciones de 2027 en Chihuahua</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46234.91964240741</v>
+        <v>46237.6432125</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Sinaloa</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n"/>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Morena</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2065,64 +2475,48 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/sinaloa/morena-aspirantes-candidatura-sinaloa</t>
+          <t>https://elcongresista.mx/politica/chihuahua/votacion-ceresos-chihuahua-2027</t>
         </is>
       </c>
       <c r="P7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SMEE-20260731-87D95F84</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>El Congresista</t>
+          <t>Central Electoral INE</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Aldo Fasci no logra su registro para la gubernatura y alcaldía</t>
+          <t>FIMI: la amenaza contra las democracias que no respeta fronteras</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46234.91086685185</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo León</t>
-        </is>
-      </c>
+        <v>46237.625</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>PAN</t>
-        </is>
-      </c>
+      <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Registro o anuncio de candidatura</t>
+          <t>Otro evento electoral</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>classified</t>
+          <t>review</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>additional_evidence</t>
-        </is>
-      </c>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -2135,18 +2529,22 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/nuevo-leon/aldofasci-registro-gubernatura-alcaldia</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="n"/>
+          <t>https://centralelectoral.ine.mx/2026/08/03/fimi-informe-ue/</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Certeza INE</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-6A2B860E</t>
+          <t>SMEE-20260803-A2EAB4CA</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2156,25 +2554,25 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Mayra Chavez asume mesa de seguridad en Juárez a días de su candidatura</t>
+          <t>David Cortés impulsa alianzas y unidad en el PAN de Morelia</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46234.76438589121</v>
+        <v>46237.60846872685</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Chihuahua</t>
+          <t>Michoacán</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Chihuahua</t>
+          <t>Morelia</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Morena</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2184,12 +2582,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>classified</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -2209,48 +2607,40 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/chihuahua/mayra-chavez-seguridad-juarez-candidatura</t>
+          <t>https://elcongresista.mx/politica/michoacan/david-cortes-unidad-pan-morelia-2027</t>
         </is>
       </c>
       <c r="P9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260801-773DCE01</t>
+          <t>SMEE-20260803-E6C5BB3F</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Central Electoral INE</t>
+          <t>El Universal Estados</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>INE aprueba plan integral y calendario del Proceso Electoral Federal 2026-2027</t>
+          <t>Ulises Mejía Haro consolida ventaja hacia gubernatura | El Universal</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46234.74109953704</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
+        <v>46237.6001088643</v>
+      </c>
+      <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Publicación oficial de calendario electoral</t>
-        </is>
-      </c>
+      <c r="I10" s="2" t="n"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>classified</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2260,7 +2650,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>additional_evidence</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -2270,37 +2660,37 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2026/07/31/ine-aprueba-plan-integral-y-calendario-del-proceso-electoral-federal-2026-2027/</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>INE</t>
-        </is>
-      </c>
+          <t>https://www.eluniversal.com.mx/estados/ulises-mejia-haro-consolida-ventaja-hacia-gubernatura/</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="n"/>
+        <v>49</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260803-49BC2B07</t>
+        </is>
+      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Central Electoral INE</t>
+          <t>Expansión Política</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Conoce como realizar las Candidaturas Independientes</t>
+          <t>Los gobernadores que ya eligieron a su sucesor para 2027: quiénes son los respaldados en los estados</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46234.71181712963</v>
+        <v>46237.6000909056</v>
       </c>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
@@ -2308,15 +2698,19 @@
       <c r="I11" s="2" t="n"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -2324,61 +2718,57 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2026/07/31/conoce-como-realizar-las-candidaturas-independientes/</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>INE</t>
-        </is>
-      </c>
+          <t>https://politica.expansion.mx/mexico/2026/07/28/gobernadores-eligieron-su-sucesor-elecciones-2027</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="2" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260803-5A7E410C</t>
+        </is>
+      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Central Electoral INE</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Invita INE Veracruz a participar en el Concurso Público 2026 para ingresar al Servicio Profesional Electoral Nacional Sistema OPLE</t>
+          <t>Morena se reúne con aspirantes a candidaturas para gobernador de Chihuahua, Sinaloa, Sonora y BC</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46234.66666666666</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Veracruz</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Xalapa</t>
-        </is>
-      </c>
+        <v>46237.60008801467</v>
+      </c>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -2386,41 +2776,37 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2026/07/31/invita-ine-veracruz-a-participar-en-el-concurso-publico-2026-para-ingresar-al-servicio-profesional-electoral-nacional-sistema-ople/</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Redacción INE</t>
-        </is>
-      </c>
+          <t>https://www.eluniversal.com.mx/nacion/morena-se-reune-con-aspirantes-a-candidaturas-para-gobernador-chihuahua-sinaloa-y-sonora-entre-ellos/</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-87D95F84</t>
+          <t>SMEE-20260803-21D35497</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>El Norte</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Fasci no logra inscribirse como candidato del PAN</t>
+          <t>“No son tiempos”: Colosio Riojas descarta adelantarse rumbo a una posible candidatura; informará decisión a finales de 2026, dice</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46234.59326388889</v>
+        <v>46237.59851851852</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -2430,22 +2816,22 @@
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>Movimiento Ciudadano</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Registro o anuncio de candidatura</t>
+          <t>Otro evento electoral</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>classified</t>
+          <t>review</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -2465,56 +2851,44 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>https://www.elnorte.com/fasci-no-logra-inscribirse-como-candidato-del-pan/ar3250331</t>
+          <t>https://www.eluniversal.com.mx/nacion/no-son-tiempos-colosio-riojas-descarta-adelantarse-rumbo-a-una-posible-candidatura-informara-decision-a-finales-de-2026-dice/</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Carlos Ortega y Miriam García</t>
+          <t>Erick  Moctezuma</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-87D95F84</t>
+          <t>SMEE-20260803-E6C5BB3F</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>El Congresista</t>
+          <t>El Universal Estados</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Aldo Fasci se registra al PAN como candidato a gobernar Nuevo León</t>
+          <t>Ulises Mejía Haro consolida ventaja hacia gubernatura | El Universal</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46234.54792417824</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo León</t>
-        </is>
-      </c>
+        <v>46237.59808311235</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>PAN</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Registro o anuncio de candidatura</t>
-        </is>
-      </c>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>classified</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2524,7 +2898,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>additional_evidence</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -2534,61 +2908,45 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/nuevo-leon/aldo-fasci-registro-pan-gobernador-nuevo-leon</t>
+          <t>https://www.eluniversal.com.mx/estados/ulises-mejia-haro-consolida-ventaja-hacia-gubernatura/</t>
         </is>
       </c>
       <c r="P14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-87D95F84</t>
+          <t>SMEE-20260803-49BC2B07</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>El Congresista</t>
+          <t>Expansión Política</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Aldo Fasci se registra como aspirante al gobierno de Monterrey</t>
+          <t>Los gobernadores que ya eligieron a su sucesor para 2027: quiénes son los respaldados en los estados</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46234.54726723379</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo León</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Monterrey</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>PAN</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Registro o anuncio de candidatura</t>
-        </is>
-      </c>
+        <v>46237.59806538164</v>
+      </c>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>classified</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2598,7 +2956,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>additional_evidence</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2608,57 +2966,45 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/nuevo-leon/aldo-fasci-registrado-monterrey</t>
+          <t>https://politica.expansion.mx/mexico/2026/07/28/gobernadores-eligieron-su-sucesor-elecciones-2027</t>
         </is>
       </c>
       <c r="P15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-2A40DFFA</t>
+          <t>SMEE-20260803-5A7E410C</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>El Congresista</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Coahuila: incertidumbre en la alianza PRI-UDC para 2027</t>
+          <t>Morena se reúne con aspirantes a candidaturas para gobernador de Chihuahua, Sinaloa, Sonora y BC</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46234.49685028935</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Coahuila</t>
-        </is>
-      </c>
+        <v>46237.59806242774</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>PRI</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Otro evento electoral</t>
-        </is>
-      </c>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>classified</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2668,62 +3014,66 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>primary_evidence</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/coahuila/coahuila-incertidumbre-alianza-pri-udc-2027</t>
+          <t>https://www.eluniversal.com.mx/nacion/morena-se-reune-con-aspirantes-a-candidaturas-para-gobernador-chihuahua-sinaloa-y-sonora-entre-ellos/</t>
         </is>
       </c>
       <c r="P16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260801-773DCE01</t>
+          <t>SMEE-20260803-E6C5BB3F</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>El Financiero</t>
+          <t>El Universal Estados</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>INE dará banderazo a las elecciones 2027 el próximo septiembre</t>
+          <t>Ulises Mejía Haro consolida ventaja hacia gubernatura | El Universal</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46234.41584490741</v>
+        <v>46237.59500083554</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n"/>
+          <t>Zacatecas</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>Morena</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Publicación oficial de calendario electoral</t>
+          <t>Registro o anuncio de candidatura</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2738,12 +3088,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>additional_evidence</t>
+          <t>primary_evidence</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2753,47 +3103,39 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>https://www.elfinanciero.com.mx/nacional/2026/07/31/ine-dara-banderazo-a-las-elecciones-2027-el-proximo-septiembre/</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Fernando Merino</t>
-        </is>
-      </c>
+          <t>https://www.eluniversal.com.mx/estados/ulises-mejia-haro-consolida-ventaja-hacia-gubernatura/</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-6059CD3E</t>
+          <t>SMEE-20260803-49BC2B07</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>El Congresista</t>
+          <t>Expansión Política</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Fracturas en la alianza Morena-PVEM crean incertidumbre electoral</t>
+          <t>Los gobernadores que ya eligieron a su sucesor para 2027: quiénes son los respaldados en los estados</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46234.38057318287</v>
+        <v>46237.59498476415</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Colima</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Colima</t>
-        </is>
-      </c>
+          <t>Michoacán</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Morena</t>
@@ -2831,61 +3173,61 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/colima/fracturas-en-la-alianza-morena-pvem</t>
+          <t>https://politica.expansion.mx/mexico/2026/07/28/gobernadores-eligieron-su-sucesor-elecciones-2027</t>
         </is>
       </c>
       <c r="P18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-4E465D4E</t>
+          <t>SMEE-20260803-5A7E410C</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>El Congresista</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>PAN lidera intención de voto para gubernatura de Querétaro 2027</t>
+          <t>Morena se reúne con aspirantes a candidaturas para gobernador de Chihuahua, Sinaloa, Sonora y BC</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46234.14221928241</v>
+        <v>46237.59498217774</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Querétaro</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Querétaro</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>Morena</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Nueva encuesta</t>
+          <t>Otro evento electoral</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>classified</t>
+          <t>review</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2905,18 +3247,18 @@
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/queretaro/pan-intencion-voto-queretaro-2027</t>
+          <t>https://www.eluniversal.com.mx/nacion/morena-se-reune-con-aspirantes-a-candidaturas-para-gobernador-chihuahua-sinaloa-y-sonora-entre-ellos/</t>
         </is>
       </c>
       <c r="P19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-1918B7EB</t>
+          <t>SMEE-20260803-8F80E3E5</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2926,21 +3268,25 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Cambios en el gobierno estatal de Coahuila anticipan precampañas</t>
+          <t>PAN define estrategias electorales: Santiago De la Peña para Chihuahua</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46234.14085893518</v>
+        <v>46237.57703354167</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Coahuila</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n"/>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Morena</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2950,12 +3296,12 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>classified</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2975,49 +3321,33 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/coahuila/cambios-gobierno-coahuila-2024</t>
+          <t>https://elcongresista.mx/politica/chihuahua/pan-candidatos-electorales-chihuahua-2027</t>
         </is>
       </c>
       <c r="P20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>SMEE-20260731-3D11F8C8</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>El Congresista</t>
+          <t>El Universal Nación</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Morena y PT definirán alianza electoral en Baja California</t>
+          <t>Aspirantes seleccionados en examen de la unam bloquean insurgentes exigen respetar resultados de evaluacion en linea</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46234.03368690972</v>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Baja California</t>
-        </is>
-      </c>
+        <v>46237.56849537037</v>
+      </c>
+      <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Morena</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Coalición o alianza</t>
-        </is>
-      </c>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t>review</t>
@@ -3028,14 +3358,10 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>primary_evidence</t>
-        </is>
-      </c>
+      <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3045,37 +3371,41 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/baja-california/baja-california-alianza-morena-pt</t>
+          <t>https://www.eluniversal.com.mx/nacion/aspirantes-seleccionados-en-examen-de-la-unam-bloquean-insurgentes-exigen-respetar-resultados-de-evaluacion-en-linea/</t>
         </is>
       </c>
       <c r="P21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>El Congresista</t>
+          <t>El Norte</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>INE inicia proceso electoral 2027 el 10 de septiembre</t>
+          <t>PAN reporta 140 registros para coordinadores en NL</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46234.01445631945</v>
-      </c>
-      <c r="F22" s="2" t="n"/>
+        <v>46237.55875</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Otro evento electoral</t>
-        </is>
-      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>PAN</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>review</t>
@@ -3099,49 +3429,37 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/nacional/ine-proceso-electoral-2027</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n"/>
+          <t>https://www.elnorte.com/pan-reporta-140-registros-para-coordinadores-en-nl/ar3251593</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Ángel Charles</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SMEE-20260730-0FCDBCDD</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>El Congresista</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Recortes presupuestales debilitan OPLE para elecciones 2027</t>
+          <t>Analistas mejoran pronóstico del PIB para este año, según encuesta de Banxico; SHCP ya lo había anticipado</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46233.3806449537</v>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Colima</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Colima</t>
-        </is>
-      </c>
+        <v>46237.55144675926</v>
+      </c>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
       <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Otro evento electoral</t>
-        </is>
-      </c>
+      <c r="I23" s="2" t="n"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>review</t>
@@ -3152,14 +3470,10 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>primary_evidence</t>
-        </is>
-      </c>
+      <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3169,67 +3483,51 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/colima/recortes-ople-elecciones-2027</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="n"/>
+          <t>https://www.eluniversal.com.mx/cartera/analistas-mejoran-pronostico-del-pib-para-este-ano-segun-encuesta-de-banxico-shcp-ya-lo-habia-anticipado/</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>Leonor Flores null</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SMEE-20260730-4E0930D8</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>El Congresista</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Somos México impugna reforma electoral en San Luis Potosí</t>
+          <t>Edson Álvarez despierta interés en Europa: estos son los tres clubes que lo buscan</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46233.34743726852</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>San Luis Potosí</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>San Luis Potosí</t>
-        </is>
-      </c>
+        <v>46237.54780092592</v>
+      </c>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
       <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Impugnación</t>
-        </is>
-      </c>
+      <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>classified</t>
+          <t>review</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>primary_evidence</t>
-        </is>
-      </c>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3239,79 +3537,1711 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/san-luis-potosi/somos-mexico-impugna-reforma-electoral-slp</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="n"/>
+          <t>https://www.eluniversal.com.mx/deportes/edson-alvarez-despierta-interes-en-europa-estos-son-los-tres-clubes-que-lo-buscan/</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Leobardo Vázquez Hernández</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SMEE-20260730-0DBCEBC0</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B25" s="2" t="n"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>El Congresista</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>INE solicita más de 36 mil millones de pesos para elecciones 2027</t>
+          <t>Sheinbaum alista reunión con Sección 22 de la CNTE sobre acuerdos en Oaxaca; prevé arranque de consulta escuela por escuela</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46233.2014409375</v>
+        <v>46237.45150462963</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Oaxaca</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.eluniversal.com.mx/nacion/sheinbaum-alista-reunion-con-seccion-22-de-la-cnte-sobre-acuerdos-en-oaxaca-preve-arranque-de-consulta-escuela-por-escuela/</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Salvador  Corona, Pedro  Villa y Caña</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260803-79036C52</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Candidaturas de Morena se afianzan en Chihuahua con nuevos registros</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>46237.42397607639</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>Otro evento electoral</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>primary_evidence</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>https://elcongresista.mx/politica/chihuahua/morena-chihuahua-registros-candidaturas</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Pemex cierra Pozo Krem-1 y continúa con programas de salud</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>46237.3245740162</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>https://elcongresista.mx/politica/veracruz/pemex-cierra-pozo-krem-1-salud-benedicto-juarez</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260803-F0C70DA7</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Morena establece nueva evaluación de candidatos para 2027</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>46237.30557045139</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Otro evento electoral</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>classified</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>primary_evidence</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O25" s="4" t="inlineStr">
-        <is>
-          <t>https://elcongresista.mx/politica/nacional/ine-presupuesto-2027</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="n"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>https://elcongresista.mx/politica/puebla/morena-filtro-candidatos-puebla-2027</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260803-C31C484D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Andrés Manuel López Beltrán recorre Distrito 6 de Tabasco</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>46237.23529333333</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Otro evento electoral</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>classified</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>primary_evidence</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>https://elcongresista.mx/politica/nacional/andres-manuel-lopez-beltran-recorrido-tabasco</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>PT traza estrategia electoral hacia 2027 en Encerrona Nacional</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>46237.12855825231</v>
+      </c>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Partido del Trabajo</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>https://elcongresista.mx/politica/nacional/encerrona-nacional-pt-2027</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>El Financiero</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>‘Andy’ López Beltrán inicia gira ‘casa por casa’ por diputación en Tabasco</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>46237.10145833333</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elfinanciero.com.mx/estados/2026/08/02/andy-lopez-beltran-inicia-gira-casa-por-casa-por-diputacion-en-tabasco/</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>Redacción</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260803-C9DFFDB0</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Andy López Beltrán inicia su camino hacia diputación federal en Tabasco</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>46237.06389490741</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Otro evento electoral</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>classified</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>primary_evidence</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>https://elcongresista.mx/politica/nacional/andy-lopez-beltran-diputado-tabasco</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260803-DF903415</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Torres Piña consolida su liderazgo en Morelia con 2 mil asistentes</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>46237.0555790625</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Morelia</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Otro evento electoral</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>classified</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>primary_evidence</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>https://elcongresista.mx/politica/michoacan/torres-pina-liderazgo-morelia</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Coahuila y Manolo Jiménez sobresalen en aprobación estatal nacional</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>46237.05407679398</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>https://elcongresista.mx/politica/coahuila/coahuila-manolo-jimenez-aprobacion</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260802-8E279CC1</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Cuatro finalistas de Morena avanzan a la encuesta estatal en CDMX</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>46236.95389979167</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Ciudad de México</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Nueva encuesta</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>classified</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>primary_evidence</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>https://elcongresista.mx/politica/nacional/cuatro-finalistas-morena-encuesta-coordinacion-estatal</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Central Electoral INE</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Fortalecen Coordinación Interinstitucional en Materia de Búsqueda de Personas en Durango</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>46236.85416666666</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>https://centralelectoral.ine.mx/2026/08/02/fortalecen-coordinacion-interinstitucional-en-materia-de-busqueda-de-personas-en-durango/</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>Redacción INE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260802-9DEC0C3C</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo León: morenistas inician contienda por gubernatura 2027</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>46236.71268537037</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Registro o anuncio de candidatura</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>classified</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>primary_evidence</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>https://elcongresista.mx/politica/nuevo-leon/nuevo-leon-morenistas-candidatura-gubernatura-2027</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Central Electoral INE</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Firma INE San Luis Potosí convenio con la Secretaría de Seguridad y Protección Ciudadana para impulsar la credencialización de personas privadas de la libertad</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>46236.625</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>https://centralelectoral.ine.mx/2026/08/02/firma-ine-san-luis-potosi-convenio-con-la-secretaria-de-seguridad-y-proteccion-ciudadana-para-impulsar-la-credencializacion-de-personas-privadas-de-la-libertad/</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>Redacción INE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260802-5E507918</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Unidad interna en Morena busca fortalecer candidatura en Chihuahua</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>46236.4322178588</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Otro evento electoral</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>primary_evidence</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>https://elcongresista.mx/politica/chihuahua/unidad-morena-chihuahua-2027</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Somos México alcanza 11 mil afiliados en Chihuahua, asegura Paty Terrazas</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>46236.42244148148</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>https://elcongresista.mx/politica/chihuahua/somos-mexico-afiliados-chihuahua</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>El Universal Nación</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Territorium retiene evidencias de trampas en examen de la unam contrato la faculta para almacenar audio y video de aspirantes</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>46236.14015046296</v>
+      </c>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.eluniversal.com.mx/nacion/territorium-retiene-evidencias-de-trampas-en-examen-de-la-unam-contrato-la-faculta-para-almacenar-audio-y-video-de-aspirantes/</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Expansión Política</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>¿Quiénes son los aspirantes a candidatos de Morena para Nayarit?</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>46236.06143518518</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>https://politica.expansion.mx/estados/2026/08/01/quienes-son-los-aspirantes-a-candidatos-de-morena-para-nayarit</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Carina García</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Expansión Política</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>¿Quiénes son los aspirantes a candidatos de Morena para Sonora?</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>46236.06011574074</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>https://politica.expansion.mx/estados/2026/08/01/quienes-son-aspirantes-candidatos-morena-sonora</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>Carina García</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Central Electoral INE</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>El INE concluye con éxito la aplicación de la prueba psicométrica del Concurso Público para ingresar al SPEN en todo el país</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>46235.9874537037</v>
+      </c>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>https://centralelectoral.ine.mx/2026/08/01/el-ine-concluye-con-exito-la-aplicacion-de-la-prueba-psicometrica-del-concurso-publico-para-ingresar-al-spen-en-todo-el-pais/</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>INE Redacción</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Homenaje póstumo a Claudio Bres Garza en Coahuila</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>46235.90934797454</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>PRI</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>https://elcongresista.mx/politica/coahuila/homenaje-claudio-bres-garza-coahuila</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Central Electoral INE</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Convocan a la ciudadanía tabasqueña a participar en el concurso público del sistema OPLE</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>46235.85416666666</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>https://centralelectoral.ine.mx/2026/08/01/convocan-a-la-ciudadania-tabasquena-a-participar-en-el-concurso-publico-del-sistema-ople/</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>Redacción INE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260801-9279F5F3</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Morena define rumbo en Michoacán para candidatura gubernamental</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>46235.84953381945</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Morelia</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Registro o anuncio de candidatura</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>classified</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>primary_evidence</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>https://elcongresista.mx/politica/michoacan/morena-candidatura-michoacan-septiembre</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Central Electoral INE</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Abre INE convocatoria para ingresar al Servicio Profesional Electoral en plazas de Institutos Electorales Estatales</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>46235.66666666666</v>
+      </c>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>https://centralelectoral.ine.mx/2026/08/01/abre-ine-convocatoria-para-ingresar-al-servicio-profesional-electoral-en-plazas-de-institutos-electorales-estatales/</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>Redacción INE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Central Electoral INE</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Aprueba Comisión de Vinculación el calendario de entrevistas para personas aspirantes a Presidencias y Consejerías Electorales de Organismos Públicos Locales</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>46235.06549768519</v>
+      </c>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>https://centralelectoral.ine.mx/2026/07/31/aprueba-comision-de-vinculacion-el-calendario-de-entrevistas-para-personas-aspirantes-a-presidencias-y-consejerias-electorales-de-organismos-publicos-locales/</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>INE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SMEE-20260801-FC0313F6</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Central Electoral INE</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Planeará y organizará INE más de 500 actividades del Proceso Electoral Federal 2026‑2027</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>46235.00425925926</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Publicación oficial de calendario electoral</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>classified</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>primary_evidence</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>https://centralelectoral.ine.mx/2026/07/31/planeara-y-organizara-ine-mas-de-500-actividades-del-proceso-electoral-federal-2026%e2%80%912027/</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>INE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Central Electoral INE</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista del Consejero Electoral Uuc-kib Espadas con Verónica Méndez para W Radio</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>46234.92717592593</v>
+      </c>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Otro evento electoral</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>https://centralelectoral.ine.mx/2026/07/31/entrevista-del-consejero-electoral-uuc-kib-espadas-con-veronica-mendez-para-w-radio/</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>INE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P25"/>
+  <autoFilter ref="A1:P51"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -3337,10 +5267,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId51"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3351,7 +5307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3403,12 +5359,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260730-0DBCEBC0</t>
+          <t>SMEE-20260801-FC0313F6</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>INE solicita más de 36 mil millones de pesos para elecciones 2027</t>
+          <t>Planeará y organizará INE más de 500 actividades del Proceso Electoral Federal 2026‑2027</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -3432,71 +5388,34 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SMEE-20260731-87D95F84</t>
+          <t>SMEE-20260803-5A7E410C</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Fasci no logra inscribirse como candidato del PAN</t>
+          <t>Morena se reúne con aspirantes a candidaturas para gobernador de Chihuahua, Sinaloa, Sonora y BC</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Aldo Fasci</t>
+          <t>Instituto Nacional Electoral</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>political</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>PAN</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo León</t>
-        </is>
-      </c>
+          <t>institution</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SMEE-20260801-773DCE01</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Planeará y organizará INE más de 500 actividades del Proceso Electoral Federal 2026‑2027</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Instituto Nacional Electoral</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>institution</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3510,7 +5429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3561,21 +5480,21 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Recortes presupuestales debilitan OPLE para elecciones 2027</t>
+          <t>“No son tiempos”: Colosio Riojas descarta adelantarse rumbo a una posible candidatura; informará decisión a finales de 2026, dice</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>El Congresista</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Colima</t>
+          <t>Nuevo León</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -3585,98 +5504,94 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Varios tipos de evento obtuvieron puntuaciones equivalentes</t>
+          <t>Se detectaron varias entidades con fuerza similar · Varios tipos de evento obtuvieron puntuaciones equivalentes</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/colima/recortes-ople-elecciones-2027</t>
+          <t>https://www.eluniversal.com.mx/nacion/no-son-tiempos-colosio-riojas-descarta-adelantarse-rumbo-a-una-posible-candidatura-informara-decision-a-finales-de-2026-dice/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>INE inicia proceso electoral 2027 el 10 de septiembre</t>
+          <t>Entrevista del Consejero Electoral Uuc-kib Espadas con Carlos Zúñiga para Milenio TV</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>El Congresista</t>
+          <t>Central Electoral INE</t>
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Otro evento electoral</t>
-        </is>
-      </c>
+      <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>No se detectó una entidad federativa · Falta entidad o ámbito geográfico</t>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · No se detectó una entidad federativa · Falta el tipo de evento o una fecha verificable</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/nacional/ine-proceso-electoral-2027</t>
+          <t>https://centralelectoral.ine.mx/2026/08/03/entrevista-del-consejero-electoral-uuc-kib-espadas-con-carlos-zuniga-para-milenio-tv-5/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Morena y PT definirán alianza electoral en Baja California</t>
+          <t>Ulises Mejía Haro consolida ventaja hacia gubernatura | El Universal</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>El Congresista</t>
+          <t>El Universal Estados</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Baja California</t>
+          <t>Zacatecas</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Coalición o alianza</t>
+          <t>Registro o anuncio de candidatura</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Se detectaron varios partidos con fuerza similar</t>
+          <t>Varios tipos de evento obtuvieron puntuaciones equivalentes</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/baja-california/baja-california-alianza-morena-pt</t>
+          <t>https://www.eluniversal.com.mx/estados/ulises-mejia-haro-consolida-ventaja-hacia-gubernatura/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Cambios en el gobierno estatal de Coahuila anticipan precampañas</t>
+          <t>Los gobernadores que ya eligieron a su sucesor para 2027: quiénes son los respaldados en los estados</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>El Congresista</t>
+          <t>Expansión Política</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Coahuila</t>
+          <t>Michoacán</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -3686,32 +5601,32 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Se detectaron varios partidos con fuerza similar</t>
+          <t>Varios tipos de evento obtuvieron puntuaciones equivalentes</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/coahuila/cambios-gobierno-coahuila-2024</t>
+          <t>https://politica.expansion.mx/mexico/2026/07/28/gobernadores-eligieron-su-sucesor-elecciones-2027</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Fracturas en la alianza Morena-PVEM crean incertidumbre electoral</t>
+          <t>Morena se reúne con aspirantes a candidaturas para gobernador de Chihuahua, Sinaloa, Sonora y BC</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>El Congresista</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Colima</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -3721,102 +5636,86 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Se detectaron varios partidos con fuerza similar</t>
+          <t>Se detectaron varias entidades con fuerza similar</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/colima/fracturas-en-la-alianza-morena-pvem</t>
+          <t>https://www.eluniversal.com.mx/nacion/morena-se-reune-con-aspirantes-a-candidaturas-para-gobernador-chihuahua-sinaloa-y-sonora-entre-ellos/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Mayra Chavez asume mesa de seguridad en Juárez a días de su candidatura</t>
+          <t>Territorium retiene evidencias de trampas en examen de la unam contrato la faculta para almacenar audio y video de aspirantes</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>El Congresista</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Chihuahua</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Otro evento electoral</t>
-        </is>
-      </c>
+          <t>El Universal Nación</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Varios tipos de evento obtuvieron puntuaciones equivalentes</t>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · No se detectó una entidad federativa · Falta el tipo de evento o una fecha verificable</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>https://elcongresista.mx/politica/chihuahua/mayra-chavez-seguridad-juarez-candidatura</t>
+          <t>https://www.eluniversal.com.mx/nacion/territorium-retiene-evidencias-de-trampas-en-examen-de-la-unam-contrato-la-faculta-para-almacenar-audio-y-video-de-aspirantes/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>INE dará banderazo a las elecciones 2027 el próximo septiembre</t>
+          <t>Aspirantes seleccionados en examen de la unam bloquean insurgentes exigen respetar resultados de evaluacion en linea</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>El Financiero</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Publicación oficial de calendario electoral</t>
-        </is>
-      </c>
+          <t>El Universal Nación</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Se detectaron varios partidos con fuerza similar</t>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · No se detectó una entidad federativa · Falta el tipo de evento o una fecha verificable</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>https://www.elfinanciero.com.mx/nacional/2026/07/31/ine-dara-banderazo-a-las-elecciones-2027-el-proximo-septiembre/</t>
+          <t>https://www.eluniversal.com.mx/nacion/aspirantes-seleccionados-en-examen-de-la-unam-bloquean-insurgentes-exigen-respetar-resultados-de-evaluacion-en-linea/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Invita INE Veracruz a participar en el Concurso Público 2026 para ingresar al Servicio Profesional Electoral Nacional Sistema OPLE</t>
+          <t>Homenaje póstumo a Claudio Bres Garza en Coahuila</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Central Electoral INE</t>
+          <t>El Congresista</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Veracruz</t>
+          <t>Coahuila</t>
         </is>
       </c>
       <c r="E9" s="5" t="n"/>
@@ -3827,107 +5726,119 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2026/07/31/invita-ine-veracruz-a-participar-en-el-concurso-publico-2026-para-ingresar-al-servicio-profesional-electoral-nacional-sistema-ople/</t>
+          <t>https://elcongresista.mx/politica/coahuila/homenaje-claudio-bres-garza-coahuila</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Conoce como realizar las Candidaturas Independientes</t>
+          <t>Somos México alcanza 11 mil afiliados en Chihuahua, asegura Paty Terrazas</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Central Electoral INE</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n"/>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>No se alcanzó el umbral para clasificar el tipo de evento · No se detectó una entidad federativa · Falta el tipo de evento o una fecha verificable</t>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · Falta el tipo de evento o una fecha verificable</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2026/07/31/conoce-como-realizar-las-candidaturas-independientes/</t>
+          <t>https://elcongresista.mx/politica/chihuahua/somos-mexico-afiliados-chihuahua</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Entrevista del Consejero Electoral Uuc-kib Espadas con Salvador García Soto para «A la una»</t>
+          <t>Unidad interna en Morena busca fortalecer candidatura en Chihuahua</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Central Electoral INE</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Otro evento electoral</t>
+        </is>
+      </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>No se alcanzó el umbral para clasificar el tipo de evento · No se detectó una entidad federativa · Falta el tipo de evento o una fecha verificable</t>
+          <t>Varios tipos de evento obtuvieron puntuaciones equivalentes</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2026/07/31/entrevista-del-consejero-electoral-uuc-kib-espadas-con-salvador-garcia-soto-para-a-la-una/</t>
+          <t>https://elcongresista.mx/politica/chihuahua/unidad-morena-chihuahua-2027</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Entrevista del Consejero Electoral Uuc-kib Espadas con Verónica Méndez para W Radio</t>
+          <t>Coahuila y Manolo Jiménez sobresalen en aprobación estatal nacional</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Central Electoral INE</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Otro evento electoral</t>
-        </is>
-      </c>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>No se detectó una entidad federativa · Falta entidad o ámbito geográfico</t>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · Falta el tipo de evento o una fecha verificable</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2026/07/31/entrevista-del-consejero-electoral-uuc-kib-espadas-con-veronica-mendez-para-w-radio/</t>
+          <t>https://elcongresista.mx/politica/coahuila/coahuila-manolo-jimenez-aprobacion</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Aprueba Comisión de Vinculación el calendario de entrevistas para personas aspirantes a Presidencias y Consejerías Electorales de Organismos Públicos Locales</t>
+          <t>PT traza estrategia electoral hacia 2027 en Encerrona Nacional</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Central Electoral INE</t>
+          <t>El Congresista</t>
         </is>
       </c>
       <c r="D13" s="5" t="n"/>
@@ -3939,12 +5850,585 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
+          <t>https://elcongresista.mx/politica/nacional/encerrona-nacional-pt-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Pemex cierra Pozo Krem-1 y continúa con programas de salud</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · Falta el tipo de evento o una fecha verificable</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>https://elcongresista.mx/politica/veracruz/pemex-cierra-pozo-krem-1-salud-benedicto-juarez</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Candidaturas de Morena se afianzan en Chihuahua con nuevos registros</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Otro evento electoral</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Varios tipos de evento obtuvieron puntuaciones equivalentes</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>https://elcongresista.mx/politica/chihuahua/morena-chihuahua-registros-candidaturas</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Morena definirá coordinador de la 4T en Sonora a finales de agosto</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>El Congresista</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · Falta el tipo de evento o una fecha verificable</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>https://elcongresista.mx/politica/sonora/morena-sonora-encuesta-coordinador-agosto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>¿Quiénes son los aspirantes a candidatos de Morena para Sonora?</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Expansión Política</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · Falta el tipo de evento o una fecha verificable</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>https://politica.expansion.mx/estados/2026/08/01/quienes-son-aspirantes-candidatos-morena-sonora</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>¿Quiénes son los aspirantes a candidatos de Morena para Nayarit?</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Expansión Política</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · Falta el tipo de evento o una fecha verificable</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>https://politica.expansion.mx/estados/2026/08/01/quienes-son-los-aspirantes-a-candidatos-de-morena-para-nayarit</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Sheinbaum alista reunión con Sección 22 de la CNTE sobre acuerdos en Oaxaca; prevé arranque de consulta escuela por escuela</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>El Universal</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · Falta el tipo de evento o una fecha verificable</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>https://www.eluniversal.com.mx/nacion/sheinbaum-alista-reunion-con-seccion-22-de-la-cnte-sobre-acuerdos-en-oaxaca-preve-arranque-de-consulta-escuela-por-escuela/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Edson Álvarez despierta interés en Europa: estos son los tres clubes que lo buscan</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>El Universal</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · No se detectó una entidad federativa · Falta el tipo de evento o una fecha verificable</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>https://www.eluniversal.com.mx/deportes/edson-alvarez-despierta-interes-en-europa-estos-son-los-tres-clubes-que-lo-buscan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Analistas mejoran pronóstico del PIB para este año, según encuesta de Banxico; SHCP ya lo había anticipado</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>El Universal</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · No se detectó una entidad federativa · Falta el tipo de evento o una fecha verificable</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>https://www.eluniversal.com.mx/cartera/analistas-mejoran-pronostico-del-pib-para-este-ano-segun-encuesta-de-banxico-shcp-ya-lo-habia-anticipado/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>PAN reporta 140 registros para coordinadores en NL</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>El Norte</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · Falta el tipo de evento o una fecha verificable</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>https://www.elnorte.com/pan-reporta-140-registros-para-coordinadores-en-nl/ar3251593</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>‘Andy’ López Beltrán inicia gira ‘casa por casa’ por diputación en Tabasco</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>El Financiero</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · Falta el tipo de evento o una fecha verificable</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>https://www.elfinanciero.com.mx/estados/2026/08/02/andy-lopez-beltran-inicia-gira-casa-por-casa-por-diputacion-en-tabasco/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Entrevista del Consejero Electoral Uuc-kib Espadas con Verónica Méndez para W Radio</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Central Electoral INE</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Otro evento electoral</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>No se detectó una entidad federativa · Falta entidad o ámbito geográfico</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>https://centralelectoral.ine.mx/2026/07/31/entrevista-del-consejero-electoral-uuc-kib-espadas-con-veronica-mendez-para-w-radio/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Aprueba Comisión de Vinculación el calendario de entrevistas para personas aspirantes a Presidencias y Consejerías Electorales de Organismos Públicos Locales</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Central Electoral INE</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · No se detectó una entidad federativa · Falta el tipo de evento o una fecha verificable</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
           <t>https://centralelectoral.ine.mx/2026/07/31/aprueba-comision-de-vinculacion-el-calendario-de-entrevistas-para-personas-aspirantes-a-presidencias-y-consejerias-electorales-de-organismos-publicos-locales/</t>
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Abre INE convocatoria para ingresar al Servicio Profesional Electoral en plazas de Institutos Electorales Estatales</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Central Electoral INE</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · No se detectó una entidad federativa · Falta el tipo de evento o una fecha verificable</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>https://centralelectoral.ine.mx/2026/08/01/abre-ine-convocatoria-para-ingresar-al-servicio-profesional-electoral-en-plazas-de-institutos-electorales-estatales/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Convocan a la ciudadanía tabasqueña a participar en el concurso público del sistema OPLE</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Central Electoral INE</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · Falta el tipo de evento o una fecha verificable</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>https://centralelectoral.ine.mx/2026/08/01/convocan-a-la-ciudadania-tabasquena-a-participar-en-el-concurso-publico-del-sistema-ople/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>El INE concluye con éxito la aplicación de la prueba psicométrica del Concurso Público para ingresar al SPEN en todo el país</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Central Electoral INE</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · No se detectó una entidad federativa · Falta el tipo de evento o una fecha verificable</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>https://centralelectoral.ine.mx/2026/08/01/el-ine-concluye-con-exito-la-aplicacion-de-la-prueba-psicometrica-del-concurso-publico-para-ingresar-al-spen-en-todo-el-pais/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Firma INE San Luis Potosí convenio con la Secretaría de Seguridad y Protección Ciudadana para impulsar la credencialización de personas privadas de la libertad</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Central Electoral INE</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · Falta el tipo de evento o una fecha verificable</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>https://centralelectoral.ine.mx/2026/08/02/firma-ine-san-luis-potosi-convenio-con-la-secretaria-de-seguridad-y-proteccion-ciudadana-para-impulsar-la-credencializacion-de-personas-privadas-de-la-libertad/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Fortalecen Coordinación Interinstitucional en Materia de Búsqueda de Personas en Durango</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Central Electoral INE</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · Falta el tipo de evento o una fecha verificable</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>https://centralelectoral.ine.mx/2026/08/02/fortalecen-coordinacion-interinstitucional-en-materia-de-busqueda-de-personas-en-durango/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>FIMI: la amenaza contra las democracias que no respeta fronteras</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Central Electoral INE</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Otro evento electoral</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>No se detectó una entidad federativa · Falta entidad o ámbito geográfico</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>https://centralelectoral.ine.mx/2026/08/03/fimi-informe-ue/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Invita INE Michoacán a la ciudadanía a recoger su Credencial para Votar</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Central Electoral INE</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>No se alcanzó el umbral para clasificar el tipo de evento · Falta el tipo de evento o una fecha verificable</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>https://centralelectoral.ine.mx/2026/08/03/invita-ine-michoacan-a-la-ciudadania-a-recoger-su-credencial-para-votar/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:G32"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -3958,10 +6442,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId32"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3972,7 +6475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4058,13 +6561,13 @@
         </is>
       </c>
       <c r="H2" s="2">
-        <f>COUNTIF('Publicaciones'!$C$2:$C$25,B2)</f>
+        <f>COUNTIF('Publicaciones'!$C$2:$C$51,B2)</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -4097,13 +6600,13 @@
         </is>
       </c>
       <c r="H3" s="2">
-        <f>COUNTIF('Publicaciones'!$C$2:$C$25,B3)</f>
+        <f>COUNTIF('Publicaciones'!$C$2:$C$51,B3)</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -4132,7 +6635,7 @@
         </is>
       </c>
       <c r="H4" s="2">
-        <f>COUNTIF('Publicaciones'!$C$2:$C$25,B4)</f>
+        <f>COUNTIF('Publicaciones'!$C$2:$C$51,B4)</f>
         <v/>
       </c>
     </row>
@@ -4167,13 +6670,13 @@
         </is>
       </c>
       <c r="H5" s="2">
-        <f>COUNTIF('Publicaciones'!$C$2:$C$25,B5)</f>
+        <f>COUNTIF('Publicaciones'!$C$2:$C$51,B5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -4206,22 +6709,22 @@
         </is>
       </c>
       <c r="H6" s="2">
-        <f>COUNTIF('Publicaciones'!$C$2:$C$25,B6)</f>
+        <f>COUNTIF('Publicaciones'!$C$2:$C$51,B6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Encuestadora Horizonte</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>pollster</t>
+          <t>media</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -4237,21 +6740,21 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>https://horizonte.example</t>
+          <t>https://www.eluniversal.com.mx</t>
         </is>
       </c>
       <c r="H7" s="2">
-        <f>COUNTIF('Publicaciones'!$C$2:$C$25,B7)</f>
+        <f>COUNTIF('Publicaciones'!$C$2:$C$51,B7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Noticias de Occidente</t>
+          <t>El Universal Estados</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -4259,14 +6762,10 @@
           <t>media</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Jalisco</t>
-        </is>
-      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4276,21 +6775,21 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>https://occidente.example</t>
+          <t>https://www.eluniversal.com.mx/estados</t>
         </is>
       </c>
       <c r="H8" s="2">
-        <f>COUNTIF('Publicaciones'!$C$2:$C$25,B8)</f>
+        <f>COUNTIF('Publicaciones'!$C$2:$C$51,B8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Panorama Nacional</t>
+          <t>El Universal Nación</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -4301,7 +6800,7 @@
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -4311,26 +6810,26 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>https://panorama.example</t>
+          <t>https://www.eluniversal.com.mx/nacion</t>
         </is>
       </c>
       <c r="H9" s="2">
-        <f>COUNTIF('Publicaciones'!$C$2:$C$25,B9)</f>
+        <f>COUNTIF('Publicaciones'!$C$2:$C$51,B9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Tribunal Electoral</t>
+          <t>Encuestadora Horizonte</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>pollster</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -4346,16 +6845,160 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
+          <t>https://horizonte.example</t>
+        </is>
+      </c>
+      <c r="H10" s="2">
+        <f>COUNTIF('Publicaciones'!$C$2:$C$51,B10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Expansión Política</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>https://politica.expansion.mx</t>
+        </is>
+      </c>
+      <c r="H11" s="2">
+        <f>COUNTIF('Publicaciones'!$C$2:$C$51,B11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Noticias de Occidente</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>https://occidente.example</t>
+        </is>
+      </c>
+      <c r="H12" s="2">
+        <f>COUNTIF('Publicaciones'!$C$2:$C$51,B12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Panorama Nacional</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>https://panorama.example</t>
+        </is>
+      </c>
+      <c r="H13" s="2">
+        <f>COUNTIF('Publicaciones'!$C$2:$C$51,B13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Tribunal Electoral</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
           <t>https://www.te.gob.mx</t>
         </is>
       </c>
-      <c r="H10" s="2">
-        <f>COUNTIF('Publicaciones'!$C$2:$C$25,B10)</f>
+      <c r="H14" s="2">
+        <f>COUNTIF('Publicaciones'!$C$2:$C$51,B14)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H10"/>
+  <autoFilter ref="A1:H14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4366,10 +7009,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
   </tableParts>
 </worksheet>
 </file>